--- a/bom/GENERIC_RB_Switch_Mechanical_BOM.xlsx
+++ b/bom/GENERIC_RB_Switch_Mechanical_BOM.xlsx
@@ -863,7 +863,7 @@
     <row r="12" ht="15" customHeight="1" s="11">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C4, C12</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="F12" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>Charger VBUS input decoupling.</t>
+          <t>C4: charger VBUS input decoupling. C12: EN-to-GND, forms an RC reset delay with R5 (10 k x 1 uF).</t>
         </is>
       </c>
     </row>
